--- a/三大アビダルマ法対照表.xlsx
+++ b/三大アビダルマ法対照表.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色法（rūpa）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心法（citta）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・遍行別境" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・善" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・煩悩" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・不定" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心不相応行法" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="無為法" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="色法（rūpa）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="心法（citta）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="心所法・遍行別境" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="心所法・善" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="心所法・煩悩" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="心所法・不定" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="心不相応行法" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="無為法" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="凡例" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>★四大種に分割</t>
+          <t>★三大種に分割</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">

--- a/三大アビダルマ法対照表.xlsx
+++ b/三大アビダルマ法対照表.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="色法（rūpa）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="心法（citta）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="心所法・遍行別境" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="心所法・善" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="心所法・煩悩" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="心所法・不定" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="心不相応行法" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="無為法" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="凡例" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色法（rūpa）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心法（citta）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・遍行別境" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・善" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・煩悩" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心所法・不定" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="心不相応行法" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="無為法" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="論点・他心知" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1333,6 +1334,257 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>記号・色分け</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>✓三系共通</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>三つの体系すべてで対応する法が存在する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>対応物なし、または特記事項あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>黄色背景</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>一つの体系に固有の法（他の二系に対応物なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>緑色背景</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>範疇移動（同じ法が異なる五位に分類されている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ピンク背景</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>上座部に対応物がない北方の煩悩心所</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>略称</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>有部</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>説一切有部（Sarvāstivāda）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>唯識</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>瑜伽行唯識学派（Yogācāra）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>上座部</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>上座部仏教（Theravāda）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>遍行</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>全ての心に伴う（universal）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>別境</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>対象を限定して生じる（object-determining）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>雑</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>善悪いずれにも生じうる（occasional/variable）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>大地法</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>有部における遍行心所（mahābhūmika）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>大善地法</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>有部における善心所（kuśala-mahābhūmika）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>大煩悩地法</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>有部における染汚遍行（kleśa-mahābhūmika）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>小煩悩地法</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>有部における限定的煩悩（parītta-kleśa-bhūmika）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>大不善地法</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>有部における不善遍行（akuśala-mahābhūmika）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>浄心所</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>上座部における美心所（sobhana cetasika）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4435,246 +4687,178 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>記号・色分け</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>意味</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>論点</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>説一切有部</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>唯識</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>上座部</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>✓三系共通</t>
+          <t>他心は何を通じて知られるか</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>三つの体系すべてで対応する法が存在する</t>
+          <t>身表・語表を手がかりに推し量る。修行で得る他心智（paracitta-jñāna）は、他者の現在の心・心所を直接の所縁とする</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>自分の識に現れた影像（相分）を通じて、間接に知る。他者の心は本質（疎所縁縁）として影像を生じさせるだけで、親所縁にはならない（「非親能了」）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>身表・語表が因となり、意門の心が他者の意図に向かう。Ganeri はこれを推論ではなく注意と読む</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>★三系で知り方が異なる。三系の外では、再認派のアビナヴァグプタが他者の主観性を直接見知ると説き、知る者は一人だという帰結に至る</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>表（vijñapti / viññatti）の身分</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>対応物なし、または特記事項あり</t>
+          <t>身表は形色、語表は声。色処・声処に含まれる実有の色法</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>表業は仮に立てたもの。実体は思（cetanā）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>身表・語表は独立の色法。身表は心から生じた風界の様態・変異で、働きは意図を示すこと</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>★上座部だけが表を独立の色法として立てる。経量部も表業の実在を認めない</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>黄色背景</t>
+          <t>他者の心と外界の身分</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>一つの体系に固有の法（他の二系に対応物なし）</t>
+          <t>他相続の心・心所も外界の色法も実有</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>外界の色法は識の変現で、識の外にはない。他者の識は実在するが、自分の識の外にある</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>他者の心も外界の色法も実在する</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>外界の実在を認める有部と上座部では、共通の世界が前提として与えられる。唯識は共相種子による共変で、共通の世界を説明する</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>緑色背景</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>範疇移動（同じ法が異なる五位に分類されている）</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>他心問題の現れ方</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>刹那滅と現在のみの実在（経量部）を厳しく取ると、他者の心を知る時点がずれる</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>外界を介さずに他者の識とどう関わるのかが問われる。後代、ラトナキールティは他相続を論駁して独我論に近づく（ダルマキールティは他相続を擁護した）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>「現在」を刹那・相続・時期の三つに分け、時期の現在（速行の長さ）を共有することで、時点のずれを避ける</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>★Ganeri の比較による整理</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ピンク背景</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>上座部に対応物がない北方の煩悩心所</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>略称</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>有部</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>説一切有部（Sarvāstivāda）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>唯識</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>瑜伽行唯識学派（Yogācāra）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>上座部</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>上座部仏教（Theravāda）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>遍行</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>全ての心に伴う（universal）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>別境</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>対象を限定して生じる（object-determining）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>雑</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>善悪いずれにも生じうる（occasional/variable）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>大地法</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>有部における遍行心所（mahābhūmika）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>大善地法</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>有部における善心所（kuśala-mahābhūmika）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>大煩悩地法</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>有部における染汚遍行（kleśa-mahābhūmika）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>小煩悩地法</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>有部における限定的煩悩（parītta-kleśa-bhūmika）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>大不善地法</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>有部における不善遍行（akuśala-mahābhūmika）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>浄心所</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>上座部における美心所（sobhana cetasika）</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>典拠</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>『倶舎論』業品（表・無表）・智品（他心智）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>『成唯識論』巻七（他心の段）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Atthasālinī（Fount）83–84・421、Visuddhimagga xiv.61–62・xiv.188、Sammohavinodanī（Dispeller）356</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>★有部・唯識の欄は記憶による整理で、原典で照合していない。整理の出発点は Ganeri『Attention, Not Self』第13章</t>
         </is>
       </c>
     </row>
